--- a/sequences/retr_trials_prc.xlsx
+++ b/sequences/retr_trials_prc.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sync_folder\TSRlearn-task\sequences\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sync_folder\TSRlearn_BIE\sequences\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -15,6 +15,7 @@
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr autoRecover="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="38">
   <si>
     <t>trial_type</t>
   </si>
@@ -83,9 +84,6 @@
     <t>distance_correct</t>
   </si>
   <si>
-    <t>stimuli/practice_images/anchor.jpg</t>
-  </si>
-  <si>
     <t>up</t>
   </si>
   <si>
@@ -93,6 +91,54 @@
   </si>
   <si>
     <t>fix_dur_retr</t>
+  </si>
+  <si>
+    <t>reflection_win_dur</t>
+  </si>
+  <si>
+    <t>ImageExamplePath</t>
+  </si>
+  <si>
+    <t>iti_dur_retr</t>
+  </si>
+  <si>
+    <t>stimuli/practice_images/practice_sequence_overview_t3_01.jpg</t>
+  </si>
+  <si>
+    <t>stimuli/practice_images/practice_sequence_overview_t3_02.jpg</t>
+  </si>
+  <si>
+    <t>stimuli/practice_images/practice_sequence_overview_t3_03.jpg</t>
+  </si>
+  <si>
+    <t>back_info_img</t>
+  </si>
+  <si>
+    <t>stimuli\practice_images\practice_sequence_overview_t3_01.jpg</t>
+  </si>
+  <si>
+    <t>stimuli\practice_images\practice_sequence_overview_t3_02.jpg</t>
+  </si>
+  <si>
+    <t>stimuli\practice_images\practice_sequence_overview_t3_03.jpg</t>
+  </si>
+  <si>
+    <t>stimuli\practice_images\practice_sequence_overview_t3_04.jpg</t>
+  </si>
+  <si>
+    <t>stimuli\practice_images\practice_sequence_overview_t3_05.jpg</t>
+  </si>
+  <si>
+    <t>stimuli\practice_images\practice_sequence_overview_t3_06.jpg</t>
+  </si>
+  <si>
+    <t>stimuli\practice_images\practice_sequence_overview_t3_07.jpg</t>
+  </si>
+  <si>
+    <t>stimuli\practice_images\practice_sequence_overview_t3_08.jpg</t>
+  </si>
+  <si>
+    <t>stimuli/practice_images/broom.jpg</t>
   </si>
 </sst>
 </file>
@@ -111,6 +157,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -159,7 +206,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -167,7 +214,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -448,10 +494,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -480,30 +526,39 @@
         <v>18</v>
       </c>
       <c r="J1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N1" t="s">
         <v>22</v>
       </c>
+      <c r="O1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G2" t="s">
         <v>8</v>
@@ -512,16 +567,28 @@
         <v>8</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>0.2</v>
+        <v>0.5</v>
+      </c>
+      <c r="L2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2">
+        <v>0.45</v>
+      </c>
+      <c r="N2">
+        <v>1.95</v>
+      </c>
+      <c r="O2" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>3</v>
       </c>
@@ -529,13 +596,22 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" t="s">
+        <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -543,16 +619,28 @@
       <c r="K3">
         <v>0.5</v>
       </c>
+      <c r="L3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3">
+        <v>0.52</v>
+      </c>
+      <c r="N3">
+        <v>1.89</v>
+      </c>
+      <c r="O3" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -564,33 +652,54 @@
         <v>11</v>
       </c>
       <c r="H4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>0.5</v>
+      </c>
+      <c r="L4" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4">
+        <v>0.61</v>
+      </c>
+      <c r="N4">
+        <v>2.15</v>
+      </c>
+      <c r="O4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" t="s">
         <v>11</v>
       </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-      <c r="J4" s="3">
-        <v>1.2</v>
-      </c>
-      <c r="K4">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
       <c r="H5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J5">
         <v>2</v>
@@ -598,25 +707,34 @@
       <c r="K5">
         <v>0.5</v>
       </c>
+      <c r="L5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5">
+        <v>0.45</v>
+      </c>
+      <c r="N5">
+        <v>1.95</v>
+      </c>
+      <c r="O5" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
       </c>
-      <c r="D6" t="s">
-        <v>13</v>
-      </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G6" t="s">
         <v>11</v>
@@ -625,138 +743,161 @@
         <v>11</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>0.2</v>
+        <v>0.5</v>
+      </c>
+      <c r="L6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M6">
+        <v>0.52</v>
+      </c>
+      <c r="N6">
+        <v>1.89</v>
+      </c>
+      <c r="O6" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
         <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
       </c>
       <c r="G7" t="s">
         <v>8</v>
       </c>
       <c r="H7" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J7">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="K7">
-        <v>0.2</v>
+        <v>0.5</v>
+      </c>
+      <c r="L7" t="s">
+        <v>27</v>
+      </c>
+      <c r="M7">
+        <v>0.61</v>
+      </c>
+      <c r="N7">
+        <v>2.15</v>
+      </c>
+      <c r="O7" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
         <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
       </c>
       <c r="G8" t="s">
         <v>8</v>
       </c>
       <c r="H8" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J8">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="K8">
-        <v>0.2</v>
+        <v>0.5</v>
+      </c>
+      <c r="L8" t="s">
+        <v>26</v>
+      </c>
+      <c r="M8">
+        <v>0.52</v>
+      </c>
+      <c r="N8">
+        <v>1.89</v>
+      </c>
+      <c r="O8" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" t="s">
         <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G9" t="s">
         <v>8</v>
       </c>
       <c r="H9" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I9">
         <v>2</v>
       </c>
       <c r="J9">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K9">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" t="s">
-        <v>20</v>
-      </c>
-      <c r="I10">
-        <v>2</v>
-      </c>
-      <c r="J10">
-        <v>2</v>
-      </c>
-      <c r="K10">
         <v>0.5</v>
+      </c>
+      <c r="L9" t="s">
+        <v>27</v>
+      </c>
+      <c r="M9">
+        <v>0.61</v>
+      </c>
+      <c r="N9">
+        <v>2.15</v>
+      </c>
+      <c r="O9" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/sequences/retr_trials_prc.xlsx
+++ b/sequences/retr_trials_prc.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="37">
   <si>
     <t>trial_type</t>
   </si>
@@ -82,9 +82,6 @@
   </si>
   <si>
     <t>distance_correct</t>
-  </si>
-  <si>
-    <t>up</t>
   </si>
   <si>
     <t>image_dur_retr</t>
@@ -526,22 +523,22 @@
         <v>18</v>
       </c>
       <c r="J1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1" t="s">
         <v>21</v>
       </c>
-      <c r="L1" t="s">
-        <v>23</v>
-      </c>
-      <c r="M1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N1" t="s">
-        <v>22</v>
-      </c>
       <c r="O1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
@@ -576,7 +573,7 @@
         <v>0.5</v>
       </c>
       <c r="L2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M2">
         <v>0.45</v>
@@ -585,7 +582,7 @@
         <v>1.95</v>
       </c>
       <c r="O2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
@@ -620,7 +617,7 @@
         <v>0.5</v>
       </c>
       <c r="L3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M3">
         <v>0.52</v>
@@ -629,7 +626,7 @@
         <v>1.89</v>
       </c>
       <c r="O3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
@@ -652,7 +649,7 @@
         <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I4">
         <v>3</v>
@@ -664,7 +661,7 @@
         <v>0.5</v>
       </c>
       <c r="L4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M4">
         <v>0.61</v>
@@ -673,7 +670,7 @@
         <v>2.15</v>
       </c>
       <c r="O4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
@@ -696,7 +693,7 @@
         <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I5">
         <v>2</v>
@@ -708,7 +705,7 @@
         <v>0.5</v>
       </c>
       <c r="L5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M5">
         <v>0.45</v>
@@ -717,7 +714,7 @@
         <v>1.95</v>
       </c>
       <c r="O5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
@@ -752,7 +749,7 @@
         <v>0.5</v>
       </c>
       <c r="L6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M6">
         <v>0.52</v>
@@ -761,7 +758,7 @@
         <v>1.89</v>
       </c>
       <c r="O6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
@@ -772,7 +769,7 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -784,7 +781,7 @@
         <v>8</v>
       </c>
       <c r="H7" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>4</v>
@@ -796,7 +793,7 @@
         <v>0.5</v>
       </c>
       <c r="L7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M7">
         <v>0.61</v>
@@ -805,7 +802,7 @@
         <v>2.15</v>
       </c>
       <c r="O7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
@@ -828,7 +825,7 @@
         <v>8</v>
       </c>
       <c r="H8" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I8">
         <v>3</v>
@@ -840,7 +837,7 @@
         <v>0.5</v>
       </c>
       <c r="L8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M8">
         <v>0.52</v>
@@ -849,7 +846,7 @@
         <v>1.89</v>
       </c>
       <c r="O8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
@@ -872,7 +869,7 @@
         <v>8</v>
       </c>
       <c r="H9" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="I9">
         <v>2</v>
@@ -884,7 +881,7 @@
         <v>0.5</v>
       </c>
       <c r="L9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M9">
         <v>0.61</v>
@@ -893,7 +890,7 @@
         <v>2.15</v>
       </c>
       <c r="O9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
